--- a/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>420</v>
+        <v>170</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.03551567174911</v>
+        <v>9.34551567174911</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>567.1054843282509</v>
+        <v>567.7954843282508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6101.832437926253</v>
+        <v>6094.417330729425</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58.9986702621333</v>
+        <v>59.07045423108768</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.03232429936758</v>
+        <v>1.913126552032254</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>net export 567.1 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
+          <t>net export 567.8 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>net output 567.11 MW vs PG-15 &gt;= 560.00 (margin +1.27 %)</t>
+          <t>net output 567.80 MW vs PG-15 &gt;= 560.00 (margin +1.39 %)</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>net heat rate 6,101.83 kJ/kWh vs PG-16 &lt;= 6,150.00 (margin +0.78 %)</t>
+          <t>net heat rate 6,094.42 kJ/kWh vs PG-16 &lt;= 6,150.00 (margin +0.90 %)</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>guarantee cover: at IG-09/IG-10 limits and this HMB's auxiliaries the net plant is 560.2 MW / 6,146 kJ/kWh vs Owner PG-15 560 MW / PG-16 6,150 kJ/kWh</t>
+          <t>guarantee cover: at IG-09/IG-10 limits and this HMB's auxiliaries the net plant is 560.9 MW / 6,139 kJ/kWh vs Owner PG-15 560 MW / PG-16 6,150 kJ/kWh</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-LDO-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3839,7 +3839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>net export 567.8 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
+          <t>CW temperature rise 6.65 K vs DP-CASE-0015 &lt;= 7.0 K (Condenser cooling water temperature rise)</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gross output 578.87 MW vs IG-09 &gt;= 572.00 (margin +1.20 %)</t>
+          <t>net export 567.8 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gross heat rate 5,977.82 kJ/kWh vs IG-10 &lt;= 6,020.00 (margin +0.70 %)</t>
+          <t>gross output 578.87 MW vs IG-09 &gt;= 572.00 (margin +1.20 %)</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>net output 567.80 MW vs PG-15 &gt;= 560.00 (margin +1.39 %)</t>
+          <t>gross heat rate 5,977.82 kJ/kWh vs IG-10 &lt;= 6,020.00 (margin +0.70 %)</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>net heat rate 6,094.42 kJ/kWh vs PG-16 &lt;= 6,150.00 (margin +0.90 %)</t>
+          <t>net output 567.80 MW vs PG-15 &gt;= 560.00 (margin +1.39 %)</t>
         </is>
       </c>
     </row>
@@ -3994,6 +3994,18 @@
         </is>
       </c>
       <c r="B15" t="inlineStr">
+        <is>
+          <t>net heat rate 6,094.42 kJ/kWh vs PG-16 &lt;= 6,150.00 (margin +0.90 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>guarantee cover: at IG-09/IG-10 limits and this HMB's auxiliaries the net plant is 560.9 MW / 6,139 kJ/kWh vs Owner PG-15 560 MW / PG-16 6,150 kJ/kWh</t>
         </is>
